--- a/hardware/expansion-board-v4/CHECKLIST-V4.10.xlsx
+++ b/hardware/expansion-board-v4/CHECKLIST-V4.10.xlsx
@@ -7085,33 +7085,33 @@
       <c r="G231" s="5" t="inlineStr"/>
     </row>
     <row r="232" ht="19" customHeight="1">
-      <c r="A232" s="2" t="inlineStr"/>
-      <c r="B232" s="3" t="inlineStr">
+      <c r="A232" s="6" t="inlineStr"/>
+      <c r="B232" s="7" t="inlineStr">
         <is>
           <t>J11</t>
         </is>
       </c>
-      <c r="C232" s="4" t="inlineStr">
+      <c r="C232" s="8" t="inlineStr">
         <is>
           <t>调试焊盘阵列 2x10</t>
         </is>
       </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="D232" s="8" t="inlineStr">
         <is>
           <t>TestPad_2x10_P2.54mm</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E232" s="6" t="inlineStr">
         <is>
           <t>55.0, 85.9</t>
         </is>
       </c>
-      <c r="F232" s="4" t="inlineStr">
-        <is>
-          <t>B MCU + Flash</t>
-        </is>
-      </c>
-      <c r="G232" s="5" t="inlineStr"/>
+      <c r="F232" s="8" t="inlineStr">
+        <is>
+          <t>不贴（调试焊盘阵列，不贴件）</t>
+        </is>
+      </c>
+      <c r="G232" s="9" t="inlineStr"/>
     </row>
     <row r="233" ht="19" customHeight="1"/>
     <row r="234" ht="19" customHeight="1">
